--- a/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -306,7 +306,7 @@
     <t>AllergyIntolerance.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -754,7 +754,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -776,7 +776,7 @@
     <t>AllergyIntolerance.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -840,7 +840,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -863,7 +863,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1438,7 +1438,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.54296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="253.93359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-allergyintolerance-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
